--- a/InputData/elec/CCaMC/Capacity Construction and Maint Costs.xlsx
+++ b/InputData/elec/CCaMC/Capacity Construction and Maint Costs.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10810"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ssy02/Desktop/Postdoc Projects/eps-brazil-cpl/InputData/elec/CCaMC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6342B638-E4B3-0541-B912-E7A2679E5820}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8392931-16A4-E044-BCB8-6B713BB659AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="780" windowWidth="34200" windowHeight="21360" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="760" windowWidth="34200" windowHeight="21380" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -818,12 +818,12 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -18395,10 +18395,10 @@
       <c r="B3" s="5">
         <v>5154</v>
       </c>
-      <c r="D3" s="58" t="s">
+      <c r="D3" s="59" t="s">
         <v>28</v>
       </c>
-      <c r="E3" s="59"/>
+      <c r="E3" s="60"/>
       <c r="F3" s="11">
         <v>0.1</v>
       </c>
@@ -18410,10 +18410,10 @@
       <c r="B4" s="5">
         <v>2.1000000000000001E-2</v>
       </c>
-      <c r="D4" s="60" t="s">
+      <c r="D4" s="61" t="s">
         <v>30</v>
       </c>
-      <c r="E4" s="59"/>
+      <c r="E4" s="60"/>
       <c r="F4" s="11">
         <v>0.41</v>
       </c>
@@ -24583,7 +24583,7 @@
       <c r="A58" s="25" t="s">
         <v>146</v>
       </c>
-      <c r="B58" s="61">
+      <c r="B58" s="58">
         <v>0.1855</v>
       </c>
       <c r="C58" s="5"/>

--- a/InputData/elec/CCaMC/Capacity Construction and Maint Costs.xlsx
+++ b/InputData/elec/CCaMC/Capacity Construction and Maint Costs.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="765" windowWidth="34200" windowHeight="21375" firstSheet="4" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="765" windowWidth="34200" windowHeight="21375" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -3229,11 +3229,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="-89761200"/>
-        <c:axId val="-89760112"/>
+        <c:axId val="1740202064"/>
+        <c:axId val="1740203152"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="-89761200"/>
+        <c:axId val="1740202064"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3276,7 +3276,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-89760112"/>
+        <c:crossAx val="1740203152"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -3284,7 +3284,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="-89760112"/>
+        <c:axId val="1740203152"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -3335,7 +3335,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="-89761200"/>
+        <c:crossAx val="1740202064"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -7509,127 +7509,127 @@
       </c>
       <c r="B14" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!B14</f>
-        <v>77260.75</v>
+        <v>6888</v>
       </c>
       <c r="C14" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!C14</f>
-        <v>76488.142500000002</v>
+        <v>6776.3850000000002</v>
       </c>
       <c r="D14" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!D14</f>
-        <v>75715.535000000003</v>
+        <v>6664.7699999999995</v>
       </c>
       <c r="E14" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!E14</f>
-        <v>74942.927500000005</v>
+        <v>6553.1550000000007</v>
       </c>
       <c r="F14" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!F14</f>
-        <v>74170.320000000007</v>
+        <v>6441.5400000000009</v>
       </c>
       <c r="G14" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!G14</f>
-        <v>73397.712499999994</v>
+        <v>6329.9250000000002</v>
       </c>
       <c r="H14" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!H14</f>
-        <v>72625.104999999996</v>
+        <v>6218.31</v>
       </c>
       <c r="I14" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!I14</f>
-        <v>71852.497499999998</v>
+        <v>6106.6949999999997</v>
       </c>
       <c r="J14" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!J14</f>
-        <v>71079.89</v>
+        <v>5995.0800000000008</v>
       </c>
       <c r="K14" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!K14</f>
-        <v>70307.282500000001</v>
+        <v>5883.4650000000001</v>
       </c>
       <c r="L14" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!L14</f>
-        <v>69534.675000000003</v>
+        <v>5771.85</v>
       </c>
       <c r="M14" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!M14</f>
-        <v>68375.763749999998</v>
+        <v>5696.880000000001</v>
       </c>
       <c r="N14" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!N14</f>
-        <v>67216.852500000008</v>
+        <v>5621.91</v>
       </c>
       <c r="O14" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!O14</f>
-        <v>66057.941250000003</v>
+        <v>5546.9400000000005</v>
       </c>
       <c r="P14" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!P14</f>
-        <v>64899.03</v>
+        <v>5471.97</v>
       </c>
       <c r="Q14" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!Q14</f>
-        <v>63740.118750000001</v>
+        <v>5397</v>
       </c>
       <c r="R14" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!R14</f>
-        <v>62581.207500000004</v>
+        <v>5322.0300000000007</v>
       </c>
       <c r="S14" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!S14</f>
-        <v>61422.296249999999</v>
+        <v>5247.06</v>
       </c>
       <c r="T14" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!T14</f>
-        <v>60263.385000000002</v>
+        <v>5172.09</v>
       </c>
       <c r="U14" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!U14</f>
-        <v>59104.473749999997</v>
+        <v>5097.12</v>
       </c>
       <c r="V14" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!V14</f>
-        <v>57945.5625</v>
+        <v>5022.1500000000005</v>
       </c>
       <c r="W14" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!W14</f>
-        <v>57945.5625</v>
+        <v>4950.4350000000004</v>
       </c>
       <c r="X14" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!X14</f>
-        <v>57945.5625</v>
+        <v>4878.72</v>
       </c>
       <c r="Y14" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!Y14</f>
-        <v>57945.5625</v>
+        <v>4807.005000000001</v>
       </c>
       <c r="Z14" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!Z14</f>
-        <v>57945.5625</v>
+        <v>4735.29</v>
       </c>
       <c r="AA14" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!AA14</f>
-        <v>57945.5625</v>
+        <v>4663.5749999999998</v>
       </c>
       <c r="AB14" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!AB14</f>
-        <v>57945.5625</v>
+        <v>4591.8599999999997</v>
       </c>
       <c r="AC14" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!AC14</f>
-        <v>57945.5625</v>
+        <v>4520.1449999999995</v>
       </c>
       <c r="AD14" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!AD14</f>
-        <v>57945.5625</v>
+        <v>4448.43</v>
       </c>
       <c r="AE14" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!AE14</f>
-        <v>57945.5625</v>
+        <v>4376.7150000000001</v>
       </c>
       <c r="AF14" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!AF14</f>
-        <v>57945.5625</v>
+        <v>4305</v>
       </c>
       <c r="AG14" s="30"/>
       <c r="AH14" s="30"/>
@@ -7956,127 +7956,127 @@
       </c>
       <c r="B17" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!B17</f>
-        <v>233952</v>
+        <v>4898.25</v>
       </c>
       <c r="C17" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!C17</f>
-        <v>233952</v>
+        <v>4898.25</v>
       </c>
       <c r="D17" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!D17</f>
-        <v>233952</v>
+        <v>4898.25</v>
       </c>
       <c r="E17" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!E17</f>
-        <v>233952</v>
+        <v>4898.25</v>
       </c>
       <c r="F17" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!F17</f>
-        <v>233952</v>
+        <v>4898.25</v>
       </c>
       <c r="G17" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!G17</f>
-        <v>233952</v>
+        <v>4898.25</v>
       </c>
       <c r="H17" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!H17</f>
-        <v>233952</v>
+        <v>4898.25</v>
       </c>
       <c r="I17" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!I17</f>
-        <v>233952</v>
+        <v>4898.25</v>
       </c>
       <c r="J17" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!J17</f>
-        <v>233952</v>
+        <v>4898.25</v>
       </c>
       <c r="K17" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!K17</f>
-        <v>233952</v>
+        <v>4898.25</v>
       </c>
       <c r="L17" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!L17</f>
-        <v>233952</v>
+        <v>4898.25</v>
       </c>
       <c r="M17" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!M17</f>
-        <v>233952</v>
+        <v>4898.25</v>
       </c>
       <c r="N17" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!N17</f>
-        <v>233952</v>
+        <v>4898.25</v>
       </c>
       <c r="O17" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!O17</f>
-        <v>233952</v>
+        <v>4898.25</v>
       </c>
       <c r="P17" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!P17</f>
-        <v>233952</v>
+        <v>4898.25</v>
       </c>
       <c r="Q17" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!Q17</f>
-        <v>233952</v>
+        <v>4898.25</v>
       </c>
       <c r="R17" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!R17</f>
-        <v>233952</v>
+        <v>4898.25</v>
       </c>
       <c r="S17" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!S17</f>
-        <v>233952</v>
+        <v>4898.25</v>
       </c>
       <c r="T17" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!T17</f>
-        <v>233952</v>
+        <v>4898.25</v>
       </c>
       <c r="U17" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!U17</f>
-        <v>233952</v>
+        <v>4898.25</v>
       </c>
       <c r="V17" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!V17</f>
-        <v>233952</v>
+        <v>4898.25</v>
       </c>
       <c r="W17" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!W17</f>
-        <v>233952</v>
+        <v>4898.25</v>
       </c>
       <c r="X17" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!X17</f>
-        <v>233952</v>
+        <v>4898.25</v>
       </c>
       <c r="Y17" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!Y17</f>
-        <v>233952</v>
+        <v>4898.25</v>
       </c>
       <c r="Z17" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!Z17</f>
-        <v>233952</v>
+        <v>4898.25</v>
       </c>
       <c r="AA17" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!AA17</f>
-        <v>233952</v>
+        <v>4898.25</v>
       </c>
       <c r="AB17" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!AB17</f>
-        <v>233952</v>
+        <v>4898.25</v>
       </c>
       <c r="AC17" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!AC17</f>
-        <v>233952</v>
+        <v>4898.25</v>
       </c>
       <c r="AD17" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!AD17</f>
-        <v>233952</v>
+        <v>4898.25</v>
       </c>
       <c r="AE17" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!AE17</f>
-        <v>233952</v>
+        <v>4898.25</v>
       </c>
       <c r="AF17" s="30">
         <f>'CCaMC-AFOaMCpUC-pre-ret'!AF17</f>
-        <v>233952</v>
+        <v>4898.25</v>
       </c>
       <c r="AG17" s="30"/>
       <c r="AH17" s="30"/>
@@ -20330,131 +20330,131 @@
       </c>
       <c r="B6" s="30">
         <f>TREND('capital processing'!$M$6:$N$6,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!B1)</f>
-        <v>909086.34666666761</v>
+        <v>1322307.413333334</v>
       </c>
       <c r="C6" s="30">
         <f>TREND('capital processing'!$M$6:$N$6,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!C1)</f>
-        <v>900680</v>
+        <v>1310080</v>
       </c>
       <c r="D6" s="30">
         <f>TREND('capital processing'!$M$6:$N$6,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!D1)</f>
-        <v>892273.65333333239</v>
+        <v>1297852.586666666</v>
       </c>
       <c r="E6" s="30">
         <f>TREND('capital processing'!$M$6:$N$6,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!E1)</f>
-        <v>883867.30666666478</v>
+        <v>1285625.1733333319</v>
       </c>
       <c r="F6" s="30">
         <f>TREND('capital processing'!$M$6:$N$6,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!F1)</f>
-        <v>875460.96000000089</v>
+        <v>1273397.7599999979</v>
       </c>
       <c r="G6" s="30">
         <f>TREND('capital processing'!$M$6:$N$6,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!G1)</f>
-        <v>867054.61333333328</v>
+        <v>1261170.3466666676</v>
       </c>
       <c r="H6" s="30">
         <f>TREND('capital processing'!$M$6:$N$6,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!H1)</f>
-        <v>858648.26666666567</v>
+        <v>1248942.9333333336</v>
       </c>
       <c r="I6" s="30">
         <f>TREND('capital processing'!$M$6:$N$6,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!I1)</f>
-        <v>850241.91999999806</v>
+        <v>1236715.5199999996</v>
       </c>
       <c r="J6" s="30">
         <f>TREND('capital processing'!$M$6:$N$6,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!J1)</f>
-        <v>841835.57333333418</v>
+        <v>1224488.1066666655</v>
       </c>
       <c r="K6" s="30">
         <f>TREND('capital processing'!$M$6:$N$6,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!K1)</f>
-        <v>833429.22666666657</v>
+        <v>1212260.6933333315</v>
       </c>
       <c r="L6" s="30">
         <f>TREND('capital processing'!$M$6:$N$6,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!L1)</f>
-        <v>825022.87999999896</v>
+        <v>1200033.2799999975</v>
       </c>
       <c r="M6" s="30">
         <f>TREND('capital processing'!$M$6:$N$6,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!M1)</f>
-        <v>816616.53333333135</v>
+        <v>1187805.8666666672</v>
       </c>
       <c r="N6" s="30">
         <f>TREND('capital processing'!$M$6:$N$6,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!N1)</f>
-        <v>808210.18666666746</v>
+        <v>1175578.4533333331</v>
       </c>
       <c r="O6" s="30">
         <f>TREND('capital processing'!$M$6:$N$6,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!O1)</f>
-        <v>799803.83999999985</v>
+        <v>1163351.0399999991</v>
       </c>
       <c r="P6" s="30">
         <f>TREND('capital processing'!$M$6:$N$6,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!P1)</f>
-        <v>791397.49333333224</v>
+        <v>1151123.6266666651</v>
       </c>
       <c r="Q6" s="30">
         <f>TREND('capital processing'!$M$6:$N$6,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!Q1)</f>
-        <v>782991.14666666463</v>
+        <v>1138896.213333331</v>
       </c>
       <c r="R6" s="30">
         <f>TREND('capital processing'!$M$6:$N$6,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!R1)</f>
-        <v>774584.80000000075</v>
+        <v>1126668.8000000007</v>
       </c>
       <c r="S6" s="30">
         <f>TREND('capital processing'!$M$6:$N$6,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!S1)</f>
-        <v>766178.45333333313</v>
+        <v>1114441.3866666667</v>
       </c>
       <c r="T6" s="30">
         <f>TREND('capital processing'!$M$6:$N$6,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!T1)</f>
-        <v>757772.10666666552</v>
+        <v>1102213.9733333327</v>
       </c>
       <c r="U6" s="30">
         <f>TREND('capital processing'!$M$6:$N$6,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!U1)</f>
-        <v>749365.75999999791</v>
+        <v>1089986.5599999987</v>
       </c>
       <c r="V6" s="30">
         <f>TREND('capital processing'!$M$6:$N$6,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!V1)</f>
-        <v>740959.41333333403</v>
+        <v>1077759.1466666646</v>
       </c>
       <c r="W6" s="30">
         <f>TREND('capital processing'!$M$6:$N$6,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!W1)</f>
-        <v>732553.06666666642</v>
+        <v>1065531.7333333306</v>
       </c>
       <c r="X6" s="30">
         <f>TREND('capital processing'!$M$6:$N$6,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!X1)</f>
-        <v>724146.71999999881</v>
+        <v>1053304.3200000003</v>
       </c>
       <c r="Y6" s="30">
         <f>TREND('capital processing'!$M$6:$N$6,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!Y1)</f>
-        <v>715740.3733333312</v>
+        <v>1041076.9066666663</v>
       </c>
       <c r="Z6" s="30">
         <f>TREND('capital processing'!$M$6:$N$6,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!Z1)</f>
-        <v>707334.02666666731</v>
+        <v>1028849.4933333322</v>
       </c>
       <c r="AA6" s="30">
         <f>TREND('capital processing'!$M$6:$N$6,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!AA1)</f>
-        <v>698927.6799999997</v>
+        <v>1016622.0799999982</v>
       </c>
       <c r="AB6" s="30">
         <f>TREND('capital processing'!$M$6:$N$6,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!AB1)</f>
-        <v>690521.33333333209</v>
+        <v>1004394.6666666642</v>
       </c>
       <c r="AC6" s="30">
         <f>TREND('capital processing'!$M$6:$N$6,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!AC1)</f>
-        <v>682114.98666666448</v>
+        <v>992167.25333333388</v>
       </c>
       <c r="AD6" s="30">
         <f>TREND('capital processing'!$M$6:$N$6,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!AD1)</f>
-        <v>673708.6400000006</v>
+        <v>979939.83999999985</v>
       </c>
       <c r="AE6" s="30">
         <f>TREND('capital processing'!$M$6:$N$6,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!AE1)</f>
-        <v>665302.29333333299</v>
+        <v>967712.42666666582</v>
       </c>
       <c r="AF6" s="30">
         <f>TREND('capital processing'!$M$6:$N$6,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!AF1)</f>
-        <v>656895.94666666538</v>
+        <v>955485.01333333179</v>
       </c>
       <c r="AG6" s="30">
         <f>TREND('capital processing'!$M$6:$N$6,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!AG1)</f>
-        <v>648489.60000000149</v>
+        <v>943257.59999999776</v>
       </c>
       <c r="AH6" s="30"/>
       <c r="AI6" s="30"/>
@@ -20483,131 +20483,131 @@
       </c>
       <c r="B7" s="30">
         <f>TREND('capital processing'!$M$7:$N$7,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!B1)</f>
-        <v>748735.59493670613</v>
+        <v>812827.00421940908</v>
       </c>
       <c r="C7" s="30">
         <f>TREND('capital processing'!$M$7:$N$7,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!C1)</f>
-        <v>736920</v>
+        <v>800000</v>
       </c>
       <c r="D7" s="30">
         <f>TREND('capital processing'!$M$7:$N$7,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!D1)</f>
-        <v>725104.40506329015</v>
+        <v>787172.9957805872</v>
       </c>
       <c r="E7" s="30">
         <f>TREND('capital processing'!$M$7:$N$7,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!E1)</f>
-        <v>713288.8101265803</v>
+        <v>774345.99156117812</v>
       </c>
       <c r="F7" s="30">
         <f>TREND('capital processing'!$M$7:$N$7,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!F1)</f>
-        <v>701473.21518987045</v>
+        <v>761518.98734176904</v>
       </c>
       <c r="G7" s="30">
         <f>TREND('capital processing'!$M$7:$N$7,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!G1)</f>
-        <v>689657.62025316432</v>
+        <v>748691.98312235996</v>
       </c>
       <c r="H7" s="30">
         <f>TREND('capital processing'!$M$7:$N$7,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!H1)</f>
-        <v>677842.02531645447</v>
+        <v>735864.97890295088</v>
       </c>
       <c r="I7" s="30">
         <f>TREND('capital processing'!$M$7:$N$7,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!I1)</f>
-        <v>666026.43037974462</v>
+        <v>723037.9746835418</v>
       </c>
       <c r="J7" s="30">
         <f>TREND('capital processing'!$M$7:$N$7,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!J1)</f>
-        <v>654210.83544303477</v>
+        <v>710210.97046413273</v>
       </c>
       <c r="K7" s="30">
         <f>TREND('capital processing'!$M$7:$N$7,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!K1)</f>
-        <v>642395.24050632864</v>
+        <v>697383.96624472365</v>
       </c>
       <c r="L7" s="30">
         <f>TREND('capital processing'!$M$7:$N$7,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!L1)</f>
-        <v>630579.64556961879</v>
+        <v>684556.96202531457</v>
       </c>
       <c r="M7" s="30">
         <f>TREND('capital processing'!$M$7:$N$7,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!M1)</f>
-        <v>618764.05063290894</v>
+        <v>671729.95780590549</v>
       </c>
       <c r="N7" s="30">
         <f>TREND('capital processing'!$M$7:$N$7,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!N1)</f>
-        <v>606948.45569619909</v>
+        <v>658902.95358649641</v>
       </c>
       <c r="O7" s="30">
         <f>TREND('capital processing'!$M$7:$N$7,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!O1)</f>
-        <v>595132.86075949296</v>
+        <v>646075.94936708733</v>
       </c>
       <c r="P7" s="30">
         <f>TREND('capital processing'!$M$7:$N$7,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!P1)</f>
-        <v>583317.26582278311</v>
+        <v>633248.94514767826</v>
       </c>
       <c r="Q7" s="30">
         <f>TREND('capital processing'!$M$7:$N$7,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!Q1)</f>
-        <v>571501.67088607326</v>
+        <v>620421.94092826918</v>
       </c>
       <c r="R7" s="30">
         <f>TREND('capital processing'!$M$7:$N$7,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!R1)</f>
-        <v>559686.07594936714</v>
+        <v>607594.9367088601</v>
       </c>
       <c r="S7" s="30">
         <f>TREND('capital processing'!$M$7:$N$7,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!S1)</f>
-        <v>547870.48101265728</v>
+        <v>594767.93248945102</v>
       </c>
       <c r="T7" s="30">
         <f>TREND('capital processing'!$M$7:$N$7,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!T1)</f>
-        <v>536054.88607594743</v>
+        <v>581940.92827004194</v>
       </c>
       <c r="U7" s="30">
         <f>TREND('capital processing'!$M$7:$N$7,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!U1)</f>
-        <v>524239.29113923758</v>
+        <v>569113.92405063286</v>
       </c>
       <c r="V7" s="30">
         <f>TREND('capital processing'!$M$7:$N$7,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!V1)</f>
-        <v>512423.69620253146</v>
+        <v>556286.91983122006</v>
       </c>
       <c r="W7" s="30">
         <f>TREND('capital processing'!$M$7:$N$7,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!W1)</f>
-        <v>500608.10126582161</v>
+        <v>543459.91561181098</v>
       </c>
       <c r="X7" s="30">
         <f>TREND('capital processing'!$M$7:$N$7,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!X1)</f>
-        <v>488792.50632911175</v>
+        <v>530632.9113924019</v>
       </c>
       <c r="Y7" s="30">
         <f>TREND('capital processing'!$M$7:$N$7,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!Y1)</f>
-        <v>476976.9113924019</v>
+        <v>517805.90717299283</v>
       </c>
       <c r="Z7" s="30">
         <f>TREND('capital processing'!$M$7:$N$7,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!Z1)</f>
-        <v>465161.31645569578</v>
+        <v>504978.90295358375</v>
       </c>
       <c r="AA7" s="30">
         <f>TREND('capital processing'!$M$7:$N$7,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!AA1)</f>
-        <v>453345.72151898593</v>
+        <v>492151.89873417467</v>
       </c>
       <c r="AB7" s="30">
         <f>TREND('capital processing'!$M$7:$N$7,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!AB1)</f>
-        <v>441530.12658227608</v>
+        <v>479324.89451476559</v>
       </c>
       <c r="AC7" s="30">
         <f>TREND('capital processing'!$M$7:$N$7,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!AC1)</f>
-        <v>429714.53164556623</v>
+        <v>466497.89029535651</v>
       </c>
       <c r="AD7" s="30">
         <f>TREND('capital processing'!$M$7:$N$7,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!AD1)</f>
-        <v>417898.9367088601</v>
+        <v>453670.88607594743</v>
       </c>
       <c r="AE7" s="30">
         <f>TREND('capital processing'!$M$7:$N$7,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!AE1)</f>
-        <v>406083.34177215025</v>
+        <v>440843.88185653836</v>
       </c>
       <c r="AF7" s="30">
         <f>TREND('capital processing'!$M$7:$N$7,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!AF1)</f>
-        <v>394267.7468354404</v>
+        <v>428016.87763712928</v>
       </c>
       <c r="AG7" s="30">
         <f>TREND('capital processing'!$M$7:$N$7,'capital processing'!$M$2:$N$2,'CCaMC-BCCpUC'!AG1)</f>
-        <v>382452.15189873427</v>
+        <v>415189.8734177202</v>
       </c>
       <c r="AH7" s="30"/>
       <c r="AI7" s="30"/>
@@ -30427,12 +30427,12 @@
         <v>0.72</v>
       </c>
       <c r="M6" s="71">
-        <f t="shared" si="4"/>
-        <v>900680</v>
+        <f>M3</f>
+        <v>1310080</v>
       </c>
       <c r="N6" s="59">
         <f t="shared" si="5"/>
-        <v>648489.6</v>
+        <v>943257.59999999998</v>
       </c>
     </row>
     <row r="7" spans="1:16" ht="14.25" customHeight="1">
@@ -30474,12 +30474,12 @@
         <v>0.51898734177215189</v>
       </c>
       <c r="M7" s="71">
-        <f t="shared" si="4"/>
-        <v>736920</v>
+        <f>M14</f>
+        <v>800000</v>
       </c>
       <c r="N7" s="59">
         <f t="shared" si="5"/>
-        <v>382452.15189873416</v>
+        <v>415189.87341772154</v>
       </c>
     </row>
     <row r="8" spans="1:16" ht="14.25" customHeight="1">
@@ -30520,7 +30520,6 @@
         <v>0.8</v>
       </c>
       <c r="M8" s="71">
-        <f t="shared" si="4"/>
         <v>491280</v>
       </c>
       <c r="N8" s="59">
@@ -31864,6 +31863,9 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape" r:id="rId1"/>
+  <ignoredErrors>
+    <ignoredError sqref="M6" formula="1"/>
+  </ignoredErrors>
   <drawing r:id="rId2"/>
 </worksheet>
 </file>
@@ -46776,128 +46778,128 @@
         <v>58</v>
       </c>
       <c r="B14" s="57">
-        <f>'Projections - CPL estimations'!B95</f>
-        <v>77260.75</v>
+        <f>'Projections - CPL estimations'!B56</f>
+        <v>6888</v>
       </c>
       <c r="C14" s="57">
-        <f>'Projections - CPL estimations'!C95</f>
-        <v>76488.142500000002</v>
+        <f>'Projections - CPL estimations'!C56</f>
+        <v>6776.3850000000002</v>
       </c>
       <c r="D14" s="57">
-        <f>'Projections - CPL estimations'!D95</f>
-        <v>75715.535000000003</v>
+        <f>'Projections - CPL estimations'!D56</f>
+        <v>6664.7699999999995</v>
       </c>
       <c r="E14" s="57">
-        <f>'Projections - CPL estimations'!E95</f>
-        <v>74942.927500000005</v>
+        <f>'Projections - CPL estimations'!E56</f>
+        <v>6553.1550000000007</v>
       </c>
       <c r="F14" s="57">
-        <f>'Projections - CPL estimations'!F95</f>
-        <v>74170.320000000007</v>
+        <f>'Projections - CPL estimations'!F56</f>
+        <v>6441.5400000000009</v>
       </c>
       <c r="G14" s="57">
-        <f>'Projections - CPL estimations'!G95</f>
-        <v>73397.712499999994</v>
+        <f>'Projections - CPL estimations'!G56</f>
+        <v>6329.9250000000002</v>
       </c>
       <c r="H14" s="57">
-        <f>'Projections - CPL estimations'!H95</f>
-        <v>72625.104999999996</v>
+        <f>'Projections - CPL estimations'!H56</f>
+        <v>6218.31</v>
       </c>
       <c r="I14" s="57">
-        <f>'Projections - CPL estimations'!I95</f>
-        <v>71852.497499999998</v>
+        <f>'Projections - CPL estimations'!I56</f>
+        <v>6106.6949999999997</v>
       </c>
       <c r="J14" s="57">
-        <f>'Projections - CPL estimations'!J95</f>
-        <v>71079.89</v>
+        <f>'Projections - CPL estimations'!J56</f>
+        <v>5995.0800000000008</v>
       </c>
       <c r="K14" s="57">
-        <f>'Projections - CPL estimations'!K95</f>
-        <v>70307.282500000001</v>
+        <f>'Projections - CPL estimations'!K56</f>
+        <v>5883.4650000000001</v>
       </c>
       <c r="L14" s="57">
-        <f>'Projections - CPL estimations'!L95</f>
-        <v>69534.675000000003</v>
+        <f>'Projections - CPL estimations'!L56</f>
+        <v>5771.85</v>
       </c>
       <c r="M14" s="57">
-        <f>'Projections - CPL estimations'!M95</f>
-        <v>68375.763749999998</v>
+        <f>'Projections - CPL estimations'!M56</f>
+        <v>5696.880000000001</v>
       </c>
       <c r="N14" s="57">
-        <f>'Projections - CPL estimations'!N95</f>
-        <v>67216.852500000008</v>
+        <f>'Projections - CPL estimations'!N56</f>
+        <v>5621.91</v>
       </c>
       <c r="O14" s="57">
-        <f>'Projections - CPL estimations'!O95</f>
-        <v>66057.941250000003</v>
+        <f>'Projections - CPL estimations'!O56</f>
+        <v>5546.9400000000005</v>
       </c>
       <c r="P14" s="57">
-        <f>'Projections - CPL estimations'!P95</f>
-        <v>64899.03</v>
+        <f>'Projections - CPL estimations'!P56</f>
+        <v>5471.97</v>
       </c>
       <c r="Q14" s="57">
-        <f>'Projections - CPL estimations'!Q95</f>
-        <v>63740.118750000001</v>
+        <f>'Projections - CPL estimations'!Q56</f>
+        <v>5397</v>
       </c>
       <c r="R14" s="57">
-        <f>'Projections - CPL estimations'!R95</f>
-        <v>62581.207500000004</v>
+        <f>'Projections - CPL estimations'!R56</f>
+        <v>5322.0300000000007</v>
       </c>
       <c r="S14" s="57">
-        <f>'Projections - CPL estimations'!S95</f>
-        <v>61422.296249999999</v>
+        <f>'Projections - CPL estimations'!S56</f>
+        <v>5247.06</v>
       </c>
       <c r="T14" s="57">
-        <f>'Projections - CPL estimations'!T95</f>
-        <v>60263.385000000002</v>
+        <f>'Projections - CPL estimations'!T56</f>
+        <v>5172.09</v>
       </c>
       <c r="U14" s="57">
-        <f>'Projections - CPL estimations'!U95</f>
-        <v>59104.473749999997</v>
+        <f>'Projections - CPL estimations'!U56</f>
+        <v>5097.12</v>
       </c>
       <c r="V14" s="57">
-        <f>'Projections - CPL estimations'!V95</f>
-        <v>57945.5625</v>
+        <f>'Projections - CPL estimations'!V56</f>
+        <v>5022.1500000000005</v>
       </c>
       <c r="W14" s="57">
-        <f>'Projections - CPL estimations'!W95</f>
-        <v>57945.5625</v>
+        <f>'Projections - CPL estimations'!W56</f>
+        <v>4950.4350000000004</v>
       </c>
       <c r="X14" s="57">
-        <f>'Projections - CPL estimations'!X95</f>
-        <v>57945.5625</v>
+        <f>'Projections - CPL estimations'!X56</f>
+        <v>4878.72</v>
       </c>
       <c r="Y14" s="57">
-        <f>'Projections - CPL estimations'!Y95</f>
-        <v>57945.5625</v>
+        <f>'Projections - CPL estimations'!Y56</f>
+        <v>4807.005000000001</v>
       </c>
       <c r="Z14" s="57">
-        <f>'Projections - CPL estimations'!Z95</f>
-        <v>57945.5625</v>
+        <f>'Projections - CPL estimations'!Z56</f>
+        <v>4735.29</v>
       </c>
       <c r="AA14" s="57">
-        <f>'Projections - CPL estimations'!AA95</f>
-        <v>57945.5625</v>
+        <f>'Projections - CPL estimations'!AA56</f>
+        <v>4663.5749999999998</v>
       </c>
       <c r="AB14" s="57">
-        <f>'Projections - CPL estimations'!AB95</f>
-        <v>57945.5625</v>
+        <f>'Projections - CPL estimations'!AB56</f>
+        <v>4591.8599999999997</v>
       </c>
       <c r="AC14" s="57">
-        <f>'Projections - CPL estimations'!AC95</f>
-        <v>57945.5625</v>
+        <f>'Projections - CPL estimations'!AC56</f>
+        <v>4520.1449999999995</v>
       </c>
       <c r="AD14" s="57">
-        <f>'Projections - CPL estimations'!AD95</f>
-        <v>57945.5625</v>
+        <f>'Projections - CPL estimations'!AD56</f>
+        <v>4448.43</v>
       </c>
       <c r="AE14" s="57">
-        <f>'Projections - CPL estimations'!AE95</f>
-        <v>57945.5625</v>
+        <f>'Projections - CPL estimations'!AE56</f>
+        <v>4376.7150000000001</v>
       </c>
       <c r="AF14" s="57">
-        <f>'Projections - CPL estimations'!AF95</f>
-        <v>57945.5625</v>
+        <f>'Projections - CPL estimations'!AF56</f>
+        <v>4305</v>
       </c>
       <c r="AG14" s="45"/>
       <c r="AH14" s="45"/>
@@ -47223,128 +47225,128 @@
         <v>61</v>
       </c>
       <c r="B17" s="57">
-        <f>'Projections - CPL estimations'!B98</f>
-        <v>233952</v>
+        <f>'Projections - CPL estimations'!B59</f>
+        <v>4898.25</v>
       </c>
       <c r="C17" s="57">
-        <f>'Projections - CPL estimations'!C98</f>
-        <v>233952</v>
+        <f>'Projections - CPL estimations'!C59</f>
+        <v>4898.25</v>
       </c>
       <c r="D17" s="57">
-        <f>'Projections - CPL estimations'!D98</f>
-        <v>233952</v>
+        <f>'Projections - CPL estimations'!D59</f>
+        <v>4898.25</v>
       </c>
       <c r="E17" s="57">
-        <f>'Projections - CPL estimations'!E98</f>
-        <v>233952</v>
+        <f>'Projections - CPL estimations'!E59</f>
+        <v>4898.25</v>
       </c>
       <c r="F17" s="57">
-        <f>'Projections - CPL estimations'!F98</f>
-        <v>233952</v>
+        <f>'Projections - CPL estimations'!F59</f>
+        <v>4898.25</v>
       </c>
       <c r="G17" s="57">
-        <f>'Projections - CPL estimations'!G98</f>
-        <v>233952</v>
+        <f>'Projections - CPL estimations'!G59</f>
+        <v>4898.25</v>
       </c>
       <c r="H17" s="57">
-        <f>'Projections - CPL estimations'!H98</f>
-        <v>233952</v>
+        <f>'Projections - CPL estimations'!H59</f>
+        <v>4898.25</v>
       </c>
       <c r="I17" s="57">
-        <f>'Projections - CPL estimations'!I98</f>
-        <v>233952</v>
+        <f>'Projections - CPL estimations'!I59</f>
+        <v>4898.25</v>
       </c>
       <c r="J17" s="57">
-        <f>'Projections - CPL estimations'!J98</f>
-        <v>233952</v>
+        <f>'Projections - CPL estimations'!J59</f>
+        <v>4898.25</v>
       </c>
       <c r="K17" s="57">
-        <f>'Projections - CPL estimations'!K98</f>
-        <v>233952</v>
+        <f>'Projections - CPL estimations'!K59</f>
+        <v>4898.25</v>
       </c>
       <c r="L17" s="57">
-        <f>'Projections - CPL estimations'!L98</f>
-        <v>233952</v>
+        <f>'Projections - CPL estimations'!L59</f>
+        <v>4898.25</v>
       </c>
       <c r="M17" s="57">
-        <f>'Projections - CPL estimations'!M98</f>
-        <v>233952</v>
+        <f>'Projections - CPL estimations'!M59</f>
+        <v>4898.25</v>
       </c>
       <c r="N17" s="57">
-        <f>'Projections - CPL estimations'!N98</f>
-        <v>233952</v>
+        <f>'Projections - CPL estimations'!N59</f>
+        <v>4898.25</v>
       </c>
       <c r="O17" s="57">
-        <f>'Projections - CPL estimations'!O98</f>
-        <v>233952</v>
+        <f>'Projections - CPL estimations'!O59</f>
+        <v>4898.25</v>
       </c>
       <c r="P17" s="57">
-        <f>'Projections - CPL estimations'!P98</f>
-        <v>233952</v>
+        <f>'Projections - CPL estimations'!P59</f>
+        <v>4898.25</v>
       </c>
       <c r="Q17" s="57">
-        <f>'Projections - CPL estimations'!Q98</f>
-        <v>233952</v>
+        <f>'Projections - CPL estimations'!Q59</f>
+        <v>4898.25</v>
       </c>
       <c r="R17" s="57">
-        <f>'Projections - CPL estimations'!R98</f>
-        <v>233952</v>
+        <f>'Projections - CPL estimations'!R59</f>
+        <v>4898.25</v>
       </c>
       <c r="S17" s="57">
-        <f>'Projections - CPL estimations'!S98</f>
-        <v>233952</v>
+        <f>'Projections - CPL estimations'!S59</f>
+        <v>4898.25</v>
       </c>
       <c r="T17" s="57">
-        <f>'Projections - CPL estimations'!T98</f>
-        <v>233952</v>
+        <f>'Projections - CPL estimations'!T59</f>
+        <v>4898.25</v>
       </c>
       <c r="U17" s="57">
-        <f>'Projections - CPL estimations'!U98</f>
-        <v>233952</v>
+        <f>'Projections - CPL estimations'!U59</f>
+        <v>4898.25</v>
       </c>
       <c r="V17" s="57">
-        <f>'Projections - CPL estimations'!V98</f>
-        <v>233952</v>
+        <f>'Projections - CPL estimations'!V59</f>
+        <v>4898.25</v>
       </c>
       <c r="W17" s="57">
-        <f>'Projections - CPL estimations'!W98</f>
-        <v>233952</v>
+        <f>'Projections - CPL estimations'!W59</f>
+        <v>4898.25</v>
       </c>
       <c r="X17" s="57">
-        <f>'Projections - CPL estimations'!X98</f>
-        <v>233952</v>
+        <f>'Projections - CPL estimations'!X59</f>
+        <v>4898.25</v>
       </c>
       <c r="Y17" s="57">
-        <f>'Projections - CPL estimations'!Y98</f>
-        <v>233952</v>
+        <f>'Projections - CPL estimations'!Y59</f>
+        <v>4898.25</v>
       </c>
       <c r="Z17" s="57">
-        <f>'Projections - CPL estimations'!Z98</f>
-        <v>233952</v>
+        <f>'Projections - CPL estimations'!Z59</f>
+        <v>4898.25</v>
       </c>
       <c r="AA17" s="57">
-        <f>'Projections - CPL estimations'!AA98</f>
-        <v>233952</v>
+        <f>'Projections - CPL estimations'!AA59</f>
+        <v>4898.25</v>
       </c>
       <c r="AB17" s="57">
-        <f>'Projections - CPL estimations'!AB98</f>
-        <v>233952</v>
+        <f>'Projections - CPL estimations'!AB59</f>
+        <v>4898.25</v>
       </c>
       <c r="AC17" s="57">
-        <f>'Projections - CPL estimations'!AC98</f>
-        <v>233952</v>
+        <f>'Projections - CPL estimations'!AC59</f>
+        <v>4898.25</v>
       </c>
       <c r="AD17" s="57">
-        <f>'Projections - CPL estimations'!AD98</f>
-        <v>233952</v>
+        <f>'Projections - CPL estimations'!AD59</f>
+        <v>4898.25</v>
       </c>
       <c r="AE17" s="57">
-        <f>'Projections - CPL estimations'!AE98</f>
-        <v>233952</v>
+        <f>'Projections - CPL estimations'!AE59</f>
+        <v>4898.25</v>
       </c>
       <c r="AF17" s="57">
-        <f>'Projections - CPL estimations'!AF98</f>
-        <v>233952</v>
+        <f>'Projections - CPL estimations'!AF59</f>
+        <v>4898.25</v>
       </c>
       <c r="AG17" s="45"/>
       <c r="AH17" s="45"/>
